--- a/ABA_mining/outputs/eval/task3/staff/llama3.2/contrary_v1/Contrary(P)Body(N).xlsx
+++ b/ABA_mining/outputs/eval/task3/staff/llama3.2/contrary_v1/Contrary(P)Body(N).xlsx
@@ -33651,13 +33651,13 @@
         <v>38</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3924914675767918</v>
+        <v>0.392491</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7516339869281046</v>
+        <v>0.751634</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5156950672645739</v>
+        <v>0.515695</v>
       </c>
       <c r="O2" t="n">
         <v>0.5679999999999999</v>
@@ -33710,13 +33710,13 @@
         <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>0.391156462585034</v>
+        <v>0.391156</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7516339869281046</v>
+        <v>0.751634</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5145413870246085</v>
+        <v>0.514541</v>
       </c>
       <c r="O3" t="n">
         <v>0.5659999999999999</v>
@@ -33769,13 +33769,13 @@
         <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>0.391156462585034</v>
+        <v>0.391156</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7516339869281046</v>
+        <v>0.751634</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5145413870246085</v>
+        <v>0.514541</v>
       </c>
       <c r="O4" t="n">
         <v>0.5659999999999999</v>
